--- a/output/pdf_financials_xlsx/SIG.xlsx
+++ b/output/pdf_financials_xlsx/SIG.xlsx
@@ -3622,25 +3622,25 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.190374</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.313132</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.768597</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.11686</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.473244</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.591566</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.99257</v>
       </c>
     </row>
     <row r="93">
@@ -4479,19 +4479,19 @@
         <v>-0.048616</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>-0.663594</v>
+        <v>-0.6480939999999999</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>-0.318263</v>
+        <v>-0.067083</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>-3.173362</v>
+        <v>-2.615149</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>-7.79531</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>-5.067749</v>
+        <v>-4.226297</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>-6.927597</v>
@@ -6046,7 +6046,11 @@
           <t>Reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -6716,7 +6720,11 @@
           <t>Reserve</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -7255,7 +7263,11 @@
           <t>Reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -9452,7 +9464,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SIG.xlsx
+++ b/output/pdf_financials_xlsx/SIG.xlsx
@@ -1610,10 +1610,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.041281</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.019621</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.345586</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.041281</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.019621</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.345586</v>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.041281</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.045896</v>
+        <v>0.026275</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.031169</v>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">

--- a/output/pdf_financials_xlsx/SIG.xlsx
+++ b/output/pdf_financials_xlsx/SIG.xlsx
@@ -2657,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.022023</v>
       </c>
       <c r="F64" s="3" t="n">
         <v>0</v>
@@ -2750,16 +2750,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.009671000000000001</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.028997</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.023583</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.103983</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>0</v>
@@ -3895,31 +3895,31 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.002465</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000662</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003767</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.015247</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>-0.013921</v>
+        <v>0.003456</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.013921</v>
+        <v>-0.017153</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.017736</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.224423</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.252876</v>
       </c>
     </row>
     <row r="102">
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.028982</v>
+        <v>0.031447</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.045423</v>
+        <v>0.044761</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-0.357332</v>
@@ -8211,7 +8211,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E54" s="5" t="n">
         <v>0.002465</v>
       </c>
